--- a/tests/ficheros/calc/perdidas_grafico.xlsx
+++ b/tests/ficheros/calc/perdidas_grafico.xlsx
@@ -291,11 +291,11 @@
         </c:ser>
         <c:gapWidth val="100"/>
         <c:overlap val="0"/>
-        <c:axId val="92408118"/>
-        <c:axId val="44438054"/>
+        <c:axId val="9961562"/>
+        <c:axId val="42570849"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="92408118"/>
+        <c:axId val="9961562"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -324,7 +324,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="44438054"/>
+        <c:crossAx val="42570849"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -332,7 +332,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="44438054"/>
+        <c:axId val="42570849"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -370,7 +370,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="92408118"/>
+        <c:crossAx val="9961562"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -810,7 +810,7 @@
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader>&amp;C&amp;"Times New Roman"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman"&amp;12Page &amp;P</oddFooter>
